--- a/backend/storage/imports/Master_SBM/8. HONORARARIUM NARASUMBER PAKAR PRAKTISI PROFESIONAL.xlsx
+++ b/backend/storage/imports/Master_SBM/8. HONORARARIUM NARASUMBER PAKAR PRAKTISI PROFESIONAL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43EDE1B-0B49-4B15-8C3A-4A3EDB15EFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5768C1-C439-492A-9CF7-92B75DF83D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F24A203-F15A-43FB-856A-6BCEEDA9FCC4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>NO</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>HONORARARIUM NARASUMBER/PAKAR/PRAKTISI/PROFESIONAL</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -134,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -157,11 +160,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -169,23 +192,44 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1404752-76C0-412E-B44E-FA7F8F9BD6EC}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="57.6640625" customWidth="1"/>
@@ -512,117 +556,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7">
+        <v>8</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>-1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B4" s="2">
         <v>-2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C4" s="2">
         <v>-3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D4" s="2">
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>8.1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="D5" s="4">
         <v>1700000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>8.1999999999999993</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="8">
-        <v>330</v>
-      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>-2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D10" s="6">
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D11" s="6">
         <v>220</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:4" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:4" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
